--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_207_R21.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_207_R21.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>11.147</v>
+        <v>9.891299999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>8.691700000000001</v>
+        <v>7.7049</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4553</v>
+        <v>2.1864</v>
       </c>
       <c r="G2" t="n">
         <v>6.5481</v>
@@ -610,13 +610,13 @@
         <v>2.7834</v>
       </c>
       <c r="S2" t="n">
-        <v>2.1324</v>
+        <v>0.8766</v>
       </c>
       <c r="T2" t="n">
-        <v>1.5534</v>
+        <v>0.5665</v>
       </c>
       <c r="U2" t="n">
-        <v>0.579</v>
+        <v>0.3102</v>
       </c>
       <c r="V2" t="n">
         <v>2.0026</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0851</v>
+        <v>3.6489</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5443</v>
+        <v>2.5547</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5407999999999999</v>
+        <v>1.0942</v>
       </c>
       <c r="G3" t="n">
-        <v>4.9701</v>
+        <v>1.9212</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8954</v>
+        <v>0.9709</v>
       </c>
       <c r="I3" t="n">
-        <v>5.8656</v>
+        <v>0.9503</v>
       </c>
       <c r="J3" t="n">
-        <v>6.6181</v>
+        <v>2.536</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6925</v>
+        <v>1.3717</v>
       </c>
       <c r="L3" t="n">
-        <v>5.9256</v>
+        <v>1.1643</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.648</v>
+        <v>-0.6148</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5879</v>
+        <v>-0.4008</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.06</v>
+        <v>-0.214</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.7834</v>
+        <v>1.1598</v>
       </c>
       <c r="Q3" t="n">
-        <v>-4.639</v>
+        <v>-1.1598</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0321</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.507</v>
+        <v>0.1063</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4749</v>
+        <v>0.4617</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9304</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>1.0722</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1418</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>Z. LEDAY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0352</v>
+        <v>3.5717</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0083</v>
+        <v>1.9124</v>
       </c>
       <c r="F4" t="n">
-        <v>1.027</v>
+        <v>1.6593</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9212</v>
+        <v>0.0828</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9709</v>
+        <v>-2.45</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9503</v>
+        <v>2.5329</v>
       </c>
       <c r="J4" t="n">
-        <v>2.536</v>
+        <v>1.0769</v>
       </c>
       <c r="K4" t="n">
-        <v>1.3717</v>
+        <v>-0.8837</v>
       </c>
       <c r="L4" t="n">
-        <v>1.1643</v>
+        <v>1.9606</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.6148</v>
+        <v>-0.9941</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.4008</v>
+        <v>-1.5664</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.214</v>
+        <v>0.5723</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1598</v>
+        <v>1.6237</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3195</v>
+        <v>2.7834</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0457</v>
+        <v>-0.2792</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.4402</v>
+        <v>-0.1491</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3945</v>
+        <v>-0.13</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>2.1444</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>2.1444</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Z. LEDAY</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7729</v>
+        <v>3.4561</v>
       </c>
       <c r="E5" t="n">
-        <v>1.248</v>
+        <v>3.0161</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5249</v>
+        <v>0.4399</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0828</v>
+        <v>4.9701</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.45</v>
+        <v>-0.8954</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5329</v>
+        <v>5.8656</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0769</v>
+        <v>6.6181</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8837</v>
+        <v>0.6925</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9606</v>
+        <v>5.9256</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9941</v>
+        <v>-1.648</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5664</v>
+        <v>-1.5879</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5723</v>
+        <v>-0.06</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-4.639</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7834</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.078</v>
+        <v>0.3389</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8136</v>
+        <v>-0.0351</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2645</v>
+        <v>0.3741</v>
       </c>
       <c r="V5" t="n">
-        <v>2.1444</v>
+        <v>0.9304</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1444</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.3223</v>
+        <v>0.948</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5518</v>
+        <v>-0.789</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7705</v>
+        <v>1.7369</v>
       </c>
       <c r="G6" t="n">
         <v>1.1692</v>
@@ -922,13 +922,13 @@
         <v>2.5515</v>
       </c>
       <c r="S6" t="n">
-        <v>2.081</v>
+        <v>0.7066</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9109</v>
+        <v>0.5702</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.1364</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1797</v>
+        <v>0.2133</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1797</v>
+        <v>0.2133</v>
       </c>
       <c r="G7" t="n">
         <v>0.1573</v>
@@ -1000,13 +1000,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0224</v>
+        <v>0.056</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5195</v>
+        <v>-0.25</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0341</v>
+        <v>0.2018</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4855</v>
+        <v>-0.4519</v>
       </c>
       <c r="G8" t="n">
         <v>-0.7685</v>
@@ -1078,13 +1078,13 @@
         <v>0.6959</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0892</v>
+        <v>0.3587</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1415</v>
+        <v>0.0944</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2306</v>
+        <v>0.2642</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5361</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7107</v>
+        <v>-0.6935</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.555</v>
+        <v>-0.4371</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1556</v>
+        <v>-0.2564</v>
       </c>
       <c r="G9" t="n">
         <v>-1.4061</v>
@@ -1156,13 +1156,13 @@
         <v>0.4639</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2315</v>
+        <v>0.2486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0747</v>
+        <v>0.0433</v>
       </c>
       <c r="U9" t="n">
-        <v>0.3062</v>
+        <v>0.2054</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9809</v>
+        <v>-1.745</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0997</v>
+        <v>-1.8638</v>
       </c>
       <c r="F10" t="n">
         <v>0.1188</v>
@@ -1234,10 +1234,10 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0104</v>
+        <v>-0.7745</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U10" t="n">
         <v>-0.4129</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0326</v>
+        <v>-1.7809</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3622</v>
+        <v>-0.4802</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6704</v>
+        <v>-1.3007</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9164</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1858</v>
+        <v>0.0659</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2794</v>
+        <v>0.1614</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4652</v>
+        <v>-0.0955</v>
       </c>
       <c r="V11" t="n">
         <v>0.1418</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5706</v>
+        <v>-2.1585</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2021</v>
+        <v>-2.6556</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6315</v>
+        <v>0.4971</v>
       </c>
       <c r="G12" t="n">
         <v>-2.0012</v>
@@ -1390,13 +1390,13 @@
         <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3374</v>
+        <v>0.0747</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4402</v>
+        <v>0.1063</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1028</v>
+        <v>-0.0316</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>14.7279</v>
+        <v>15.1014</v>
       </c>
       <c r="E13" t="n">
-        <v>8.791</v>
+        <v>9.164200000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>5.937</v>
+        <v>5.9369</v>
       </c>
       <c r="G13" t="n">
-        <v>5.999899999999999</v>
+        <v>5.999900000000001</v>
       </c>
       <c r="H13" t="n">
         <v>-8.9732</v>
@@ -1459,7 +1459,7 @@
         <v>1.2727</v>
       </c>
       <c r="P13" t="n">
-        <v>2.3196</v>
+        <v>2.319599999999999</v>
       </c>
       <c r="Q13" t="n">
         <v>-15.0769</v>
@@ -1468,13 +1468,13 @@
         <v>17.3964</v>
       </c>
       <c r="S13" t="n">
-        <v>1.867100000000001</v>
+        <v>2.2403</v>
       </c>
       <c r="T13" t="n">
-        <v>0.7289999999999999</v>
+        <v>1.1027</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1378</v>
+        <v>1.138</v>
       </c>
       <c r="V13" t="n">
         <v>4.541300000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.017</v>
+        <v>1.1293</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4826</v>
+        <v>1.2467</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4655</v>
+        <v>-0.1174</v>
       </c>
       <c r="G14" t="n">
         <v>2.9867</v>
@@ -1546,13 +1546,13 @@
         <v>2.0876</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4336</v>
+        <v>-0.3213</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3181</v>
+        <v>-0.554</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1155</v>
+        <v>0.2326</v>
       </c>
       <c r="V14" t="n">
         <v>-1.0722</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B. DESSERT</t>
+          <t>S. LEE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8726</v>
+        <v>1.0888</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1286</v>
+        <v>1.1203</v>
       </c>
       <c r="F15" t="n">
-        <v>0.744</v>
+        <v>-0.0315</v>
       </c>
       <c r="G15" t="n">
-        <v>1.434</v>
+        <v>-0.5848</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0324</v>
+        <v>1.3793</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4016</v>
+        <v>-1.9641</v>
       </c>
       <c r="J15" t="n">
-        <v>1.9526</v>
+        <v>1.1909</v>
       </c>
       <c r="K15" t="n">
-        <v>1.9158</v>
+        <v>0.6792</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0368</v>
+        <v>0.5118</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5185999999999999</v>
+        <v>-1.7758</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.8834</v>
+        <v>0.7000999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3648</v>
+        <v>-2.4759</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.3917</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q15" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>0.8303</v>
+        <v>-0.1307</v>
       </c>
       <c r="T15" t="n">
-        <v>0.7275</v>
+        <v>-0.4832</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1028</v>
+        <v>0.3525</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>2.9641</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2.9641</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. LEE</t>
+          <t>B. DESSERT</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3361</v>
+        <v>0.2663</v>
       </c>
       <c r="E16" t="n">
-        <v>0.6485</v>
+        <v>-0.3432</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3124</v>
+        <v>0.6095</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5848</v>
+        <v>1.434</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3793</v>
+        <v>1.0324</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.9641</v>
+        <v>0.4016</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1909</v>
+        <v>1.9526</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6792</v>
+        <v>1.9158</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5118</v>
+        <v>0.0368</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7758</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7000999999999999</v>
+        <v>-0.8834</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.4759</v>
+        <v>0.3648</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1598</v>
+        <v>-1.3917</v>
       </c>
       <c r="Q16" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3917</v>
+        <v>1.1598</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8834</v>
+        <v>0.224</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.955</v>
+        <v>0.2557</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0716</v>
+        <v>-0.0316</v>
       </c>
       <c r="V16" t="n">
-        <v>2.9641</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>2.9641</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>K. JONES</t>
+          <t>E. YILMAZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0177</v>
+        <v>-0.5221</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5163</v>
+        <v>-0.9898</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.4987</v>
+        <v>0.4677</v>
       </c>
       <c r="G17" t="n">
-        <v>0.4087</v>
+        <v>-1.3224</v>
       </c>
       <c r="H17" t="n">
-        <v>3.2928</v>
+        <v>-0.1849</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.8841</v>
+        <v>-1.1376</v>
       </c>
       <c r="J17" t="n">
-        <v>2.96</v>
+        <v>-0.0034</v>
       </c>
       <c r="K17" t="n">
-        <v>2.7392</v>
+        <v>0.7093</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2208</v>
+        <v>-0.7127</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.5513</v>
+        <v>-1.319</v>
       </c>
       <c r="N17" t="n">
-        <v>0.5536</v>
+        <v>-0.8942</v>
       </c>
       <c r="O17" t="n">
-        <v>-3.1049</v>
+        <v>-0.4248</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.4639</v>
+        <v>0.4639</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R17" t="n">
         <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>2.359</v>
+        <v>0.1946</v>
       </c>
       <c r="T17" t="n">
-        <v>1.8758</v>
+        <v>0.2636</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4832</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-2.2862</v>
+        <v>0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.2862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9053</v>
+        <v>-0.7144</v>
       </c>
       <c r="E18" t="n">
         <v>-0.0364</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8689</v>
+        <v>-0.678</v>
       </c>
       <c r="G18" t="n">
         <v>-0.7783</v>
@@ -1858,13 +1858,13 @@
         <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0548</v>
+        <v>-0.8639</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4481</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6067</v>
+        <v>-0.4158</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>E. YILMAZ</t>
+          <t>J. LOYD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.2184</v>
+        <v>-1.0709</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.4616</v>
+        <v>-0.451</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2432</v>
+        <v>-0.6199</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.3224</v>
+        <v>-2.5905</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.1849</v>
+        <v>-2.1488</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.1376</v>
+        <v>-0.4417</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.0034</v>
+        <v>-0.4748</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7093</v>
+        <v>-1.4551</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7127</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.319</v>
+        <v>-2.1157</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8942</v>
+        <v>-0.6938</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.4248</v>
+        <v>-1.422</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8556</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5017</v>
+        <v>-0.1041</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2082</v>
+        <v>0.0237</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2934</v>
+        <v>-0.1278</v>
       </c>
       <c r="V19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. LOYD</t>
+          <t>K. JONES</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.61</v>
+        <v>-1.6552</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9229000000000001</v>
+        <v>0.865</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.6871</v>
+        <v>-2.5202</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.5905</v>
+        <v>0.4087</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.1488</v>
+        <v>3.2928</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4417</v>
+        <v>-2.8841</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4748</v>
+        <v>2.96</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.4551</v>
+        <v>2.7392</v>
       </c>
       <c r="L20" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.2208</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1157</v>
+        <v>-2.5513</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6938</v>
+        <v>0.5536</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.422</v>
+        <v>-3.1049</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6237</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6237</v>
+        <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6431</v>
+        <v>0.6862</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4481</v>
+        <v>0.2245</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.195</v>
+        <v>0.4617</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-2.2862</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.3278</v>
+        <v>-2.4292</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.0366</v>
+        <v>-1.3289</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.2912</v>
+        <v>-1.1003</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3761</v>
@@ -2092,13 +2092,13 @@
         <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4336</v>
+        <v>0.465</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.6721</v>
+        <v>0.0356</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2385</v>
+        <v>0.4294</v>
       </c>
       <c r="V21" t="n">
         <v>-1.214</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.6195</v>
+        <v>-3.5352</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.0112</v>
+        <v>-1.8933</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6083</v>
+        <v>-1.6419</v>
       </c>
       <c r="G22" t="n">
         <v>2.0424</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0382</v>
+        <v>0.0461</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2082</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>0.17</v>
+        <v>0.1364</v>
       </c>
       <c r="V22" t="n">
         <v>-2.1444</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-6.2902</v>
+        <v>-5.7126</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.2442</v>
+        <v>-4.1263</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.046</v>
+        <v>-1.5863</v>
       </c>
       <c r="G23" t="n">
         <v>-5.2197</v>
@@ -2248,13 +2248,13 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.0679</v>
+        <v>-0.4903</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4832</v>
+        <v>-0.3653</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.5847</v>
+        <v>-0.125</v>
       </c>
       <c r="V23" t="n">
         <v>-0.9304</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-14.7278</v>
+        <v>-13.1552</v>
       </c>
       <c r="E24" t="n">
-        <v>-5.936900000000001</v>
+        <v>-5.9369</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.790899999999999</v>
+        <v>-7.218299999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>-5.999999999999998</v>
+        <v>-6</v>
       </c>
       <c r="H24" t="n">
-        <v>8.9732</v>
+        <v>8.973199999999999</v>
       </c>
       <c r="I24" t="n">
         <v>-14.9734</v>
@@ -2326,13 +2326,13 @@
         <v>15.077</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.867</v>
+        <v>-0.2944</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1377</v>
+        <v>-1.1378</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.7292000000000001</v>
+        <v>0.8433999999999999</v>
       </c>
       <c r="V24" t="n">
         <v>-4.5413</v>
